--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/01010T-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/01010T-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06B87092-06E1-4D7E-ADAE-FF5BFB52B4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FCFA4E6-0785-4AF0-BBC5-B09EC8DE4AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{2511E941-0D9A-4589-8714-4CC110F5ABD1}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{401EF723-713C-4C93-8E38-967F72ABC61D}"/>
   </bookViews>
   <sheets>
     <sheet name="01010T-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1552,25 +1552,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7068037C-F14F-4790-84FF-6F4503ADCCA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{942FED54-6394-4E40-8554-82559ADB0BB9}">
   <dimension ref="A1:R30"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1598,7 +1598,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1628,7 +1628,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1724,7 +1724,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1804,7 +1804,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2026,7 +2026,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2082,7 +2082,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="49">
         <v>2023</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>27</v>
       </c>
@@ -2414,7 +2414,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>27</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="51">
         <v>2022</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>27</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>27</v>
       </c>
@@ -2636,7 +2636,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="49">
         <v>2021</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
         <v>27</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
         <v>27</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="51">
         <v>2020</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>27</v>
       </c>
@@ -2912,7 +2912,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>27</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>2019</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>27</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="51" t="s">
         <v>55</v>
       </c>
